--- a/back/resume/templates/学生数据导入模板.xlsx
+++ b/back/resume/templates/学生数据导入模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qiaoyq\IdeaProjects\resume\back\resume\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C6B6BD-610A-4FC6-9A44-6B679400FA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4E90EA-E4EC-4773-B0A8-15301C303459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EA9A6CAE-7B5B-4AB0-A130-2D1A07660662}"/>
+    <workbookView xWindow="14330" yWindow="2430" windowWidth="11470" windowHeight="11170" xr2:uid="{EA9A6CAE-7B5B-4AB0-A130-2D1A07660662}"/>
   </bookViews>
   <sheets>
     <sheet name="学生数据" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="42">
   <si>
     <t>学号</t>
   </si>
@@ -86,6 +86,94 @@
   </si>
   <si>
     <t>赵照</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李莉</t>
+  </si>
+  <si>
+    <t>女</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络工程</t>
+  </si>
+  <si>
+    <t>网络工程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能</t>
+  </si>
+  <si>
+    <t>人工智能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机科学与技术</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>软件工程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>张伟</t>
+  </si>
+  <si>
+    <t>刘洋</t>
+  </si>
+  <si>
+    <t>杨帆</t>
+  </si>
+  <si>
+    <t>黄婷婷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>周杰</t>
+  </si>
+  <si>
+    <t>吴珊珊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>郑浩然</t>
+  </si>
+  <si>
+    <t>王芳</t>
+  </si>
+  <si>
+    <t>冯坤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>韩梅梅</t>
+  </si>
+  <si>
+    <t>朱晓明</t>
+  </si>
+  <si>
+    <t>秦雨</t>
+  </si>
+  <si>
+    <t>回族</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙古族</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>朝鲜族</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>壮族</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>满族</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -468,16 +556,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95783660-81EF-4294-8B7C-07DD99366A32}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="5.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,7 +594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024081103</v>
       </c>
@@ -523,7 +611,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -535,7 +623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2024081104</v>
       </c>
@@ -552,7 +640,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -562,6 +650,383 @@
       </c>
       <c r="I3">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2024081105</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4">
+        <v>2028</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>2024081106</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>2028</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2024081107</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <v>2028</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2024081108</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>2028</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2024081109</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8">
+        <v>2028</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2024081110</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9">
+        <v>2028</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2024081111</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10">
+        <v>2028</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2024081112</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11">
+        <v>2028</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2024081113</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12">
+        <v>2028</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2024081114</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13">
+        <v>2028</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2024081115</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14">
+        <v>21</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14">
+        <v>2028</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2024081116</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15">
+        <v>2028</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2024081117</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16">
+        <v>2028</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
